--- a/out/MLP-Mamba1_repeat_5_000002.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6252523530368312</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.818340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.818340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.818340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.418340913531692</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6252523530368312</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6252523530368312</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.418340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.818340913531692</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000002.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.3690589350268096</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183546</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183546</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.4744587563681129</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183546</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183544</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183546</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.4744587563681129</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618355</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917836</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917836</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.418340913531692</v>
+        <v>0.7168981654917836</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917834</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183522</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917834</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183522</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183522</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183525</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183518</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183518</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183518</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183518</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917837</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917834</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.4744587563681129</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.4744587563681129</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618352</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917835</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618353</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183522</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.6744587563681129</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183518</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.818340913531692</v>
+        <v>0.3690589350268092</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000002.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4876934885978699</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3690589350268096</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5170390605926514</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.02121970456183546</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4670370817184448</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2212197045618355</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4788930118083954</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4955820441246033</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4992894530296326</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4681624472141266</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.02121970456183546</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.5105730295181274</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5674881935119629</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4453099071979523</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4714721143245697</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4744587563681129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4532279670238495</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.02121970456183546</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5138034820556641</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.02121970456183544</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4623643457889557</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2212197045618355</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.475949615240097</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4563416242599487</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4692939221858978</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4754462540149689</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.470398873090744</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.02121970456183546</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5106112360954285</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2212197045618355</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4540828168392181</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.2212197045618355</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4671216011047363</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4744587563681129</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4865123331546783</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2212197045618355</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6214251518249512</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2212197045618355</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4537362158298492</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5225973129272461</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5003460645675659</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.612576626421732</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5167118906974792</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4619734883308411</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4586999714374542</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4749558866024017</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4853948950767517</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4868316650390625</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4955392181873322</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5416339039802551</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7168981654917838</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.5649356245994568</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.524841845035553</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5104379653930664</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5474148988723755</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6018803715705872</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6933224201202393</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7425215244293213</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7124634981155396</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.612576626421732</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.875859260559082</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4385938942432404</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7168981654917836</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5498623847961426</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7168981654917836</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5168536305427551</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5590961575508118</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7168981654917836</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4975646138191223</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7168981654917834</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.7432684302330017</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.02121970456183522</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4624061584472656</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7168981654917834</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5911852121353149</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.02121970456183522</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4718294739723206</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.02121970456183522</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.463860809803009</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.02121970456183525</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5213242173194885</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.02121970456183518</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3932607173919678</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.02121970456183518</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4476377665996552</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.02121970456183518</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5572699308395386</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.02121970456183518</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.467730849981308</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9168981654917835</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5054903626441956</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9168981654917835</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5749721527099609</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9168981654917837</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.48200923204422</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4236362278461456</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5708935260772705</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7168981654917834</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5964974164962769</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.612576626421732</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6899309158325195</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9168981654917835</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4968678653240204</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4632126092910767</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4500041306018829</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.430905669927597</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4251589477062225</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3784809410572052</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4737186431884766</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4014015793800354</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3976885974407196</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3815798759460449</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3767593502998352</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4055602252483368</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.408867746591568</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4324260056018829</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4288634359836578</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4818172454833984</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4400362372398376</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4332965314388275</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3639015555381775</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3792480826377869</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4733310639858246</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.384308248758316</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5199530124664307</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4614293277263641</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4311980605125427</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4744587563681129</v>
+        <v>0.16</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3907933831214905</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4744587563681129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3781747817993164</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3773467242717743</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3898687958717346</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4099188148975372</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4184888899326324</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4037216603755951</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4344041049480438</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4147355258464813</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4086971879005432</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4543536603450775</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4175053536891937</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.421788364648819</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4323780536651611</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4299033582210541</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4380560219287872</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4549189805984497</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4268748462200165</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4375174641609192</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.422369658946991</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6744587563681129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4925341904163361</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5179867148399353</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4472862184047699</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4860512018203735</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2212197045618352</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5018810629844666</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9168981654917835</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.5625554919242859</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.6915189027786255</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9168981654917835</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4700514078140259</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9168981654917835</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.6312121748924255</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.2212197045618353</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4888222217559814</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.02121970456183522</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4449790418148041</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4388045370578766</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6744587563681129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4923260807991028</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.02121970456183518</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6288791298866272</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3690589350268092</v>
+        <v>-0.1599999999999997</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000002.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000002.xlsx
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.5105730295181274</v>
+        <v>0.5105729699134827</v>
       </c>
       <c r="JB9" t="n">
         <v>0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.5674881935119629</v>
+        <v>0.5674880146980286</v>
       </c>
       <c r="JB10" t="n">
         <v>0.1600000000000001</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.4453099071979523</v>
+        <v>0.4453098475933075</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.4623643457889557</v>
+        <v>0.4623644053936005</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.4563416242599487</v>
+        <v>0.4563416838645935</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.4671216011047363</v>
+        <v>0.4671216607093811</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4865123331546783</v>
+        <v>0.4865123927593231</v>
       </c>
       <c r="JB24" t="n">
         <v>0.02000000000000007</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.6214251518249512</v>
+        <v>0.6214249730110168</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4537362158298492</v>
+        <v>0.4537361264228821</v>
       </c>
       <c r="JB26" t="n">
         <v>0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.5225973129272461</v>
+        <v>0.5225972533226013</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.5003460645675659</v>
+        <v>0.5003460049629211</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4619734883308411</v>
+        <v>0.4619735479354858</v>
       </c>
       <c r="JB30" t="n">
         <v>0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4955392181873322</v>
+        <v>0.4955392777919769</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.5649356245994568</v>
+        <v>0.564935564994812</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.524841845035553</v>
+        <v>0.5248417854309082</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.5474148988723755</v>
+        <v>0.5474147796630859</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.6018803715705872</v>
+        <v>0.6018803119659424</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.6933224201202393</v>
+        <v>0.6933226585388184</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.7425215244293213</v>
+        <v>0.7425217032432556</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.7124634981155396</v>
+        <v>0.7124636173248291</v>
       </c>
       <c r="JB44" t="n">
         <v>0.1199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.875859260559082</v>
+        <v>0.8758593797683716</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.02000000000000007</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.4385938942432404</v>
+        <v>0.4385941028594971</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.5498623847961426</v>
+        <v>0.5498625636100769</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.5168536305427551</v>
+        <v>0.5168535709381104</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.5590961575508118</v>
+        <v>0.5590963363647461</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.4399999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4975646138191223</v>
+        <v>0.4975645542144775</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.7432684302330017</v>
+        <v>0.743268609046936</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.4624061584472656</v>
+        <v>0.4624063670635223</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5911852121353149</v>
+        <v>0.5911853313446045</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.4718294739723206</v>
+        <v>0.4718294143676758</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.463860809803009</v>
+        <v>0.4638607501983643</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.5213242173194885</v>
+        <v>0.5213241577148438</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.5572699308395386</v>
+        <v>0.557269811630249</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.467730849981308</v>
+        <v>0.4677308201789856</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.5054903626441956</v>
+        <v>0.5054903030395508</v>
       </c>
       <c r="JB61" t="n">
         <v>0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.5749721527099609</v>
+        <v>0.5749720931053162</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.48200923204422</v>
+        <v>0.4820091724395752</v>
       </c>
       <c r="JB63" t="n">
         <v>0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.4236362278461456</v>
+        <v>0.4236361682415009</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.5708935260772705</v>
+        <v>0.5708934664726257</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.5964974164962769</v>
+        <v>0.5964975953102112</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.6899309158325195</v>
+        <v>0.6899310350418091</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.4968678653240204</v>
+        <v>0.4968680143356323</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.4632126092910767</v>
+        <v>0.4632125496864319</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4500041306018829</v>
+        <v>0.4500040709972382</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.4251589477062225</v>
+        <v>0.4251589179039001</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4014015793800354</v>
+        <v>0.4014015197753906</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3976885974407196</v>
+        <v>0.3976886570453644</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3815798759460449</v>
+        <v>0.3815799355506897</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.4055602252483368</v>
+        <v>0.405560314655304</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.408867746591568</v>
+        <v>0.4088678359985352</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.4324260056018829</v>
+        <v>0.4324260950088501</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4400362372398376</v>
+        <v>0.4400362968444824</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.4332965314388275</v>
+        <v>0.4332965910434723</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3639015555381775</v>
+        <v>0.3639016449451447</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.2599999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3792480826377869</v>
+        <v>0.3792481422424316</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.2599999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.384308248758316</v>
+        <v>0.3843081593513489</v>
       </c>
       <c r="JB89" t="n">
         <v>0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.5199530124664307</v>
+        <v>0.5199529528617859</v>
       </c>
       <c r="JB90" t="n">
         <v>0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3781747817993164</v>
+        <v>0.3781748414039612</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3773467242717743</v>
+        <v>0.3773467540740967</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3898687958717346</v>
+        <v>0.3898689150810242</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4184888899326324</v>
+        <v>0.4184889793395996</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.4037216603755951</v>
+        <v>0.4037217199802399</v>
       </c>
       <c r="JB99" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4344041049480438</v>
+        <v>0.4344041347503662</v>
       </c>
       <c r="JB100" t="n">
         <v>0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.4086971879005432</v>
+        <v>0.4086972773075104</v>
       </c>
       <c r="JB102" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.4543536603450775</v>
+        <v>0.4543537497520447</v>
       </c>
       <c r="JB103" t="n">
         <v>0.3</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4549189805984497</v>
+        <v>0.4549190998077393</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4268748462200165</v>
+        <v>0.4268749356269836</v>
       </c>
       <c r="JB110" t="n">
         <v>0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.4375174641609192</v>
+        <v>0.4375174939632416</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4472862184047699</v>
+        <v>0.4472862780094147</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.5018810629844666</v>
+        <v>0.5018808841705322</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.5625554919242859</v>
+        <v>0.5625553131103516</v>
       </c>
       <c r="JB118" t="n">
         <v>0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.6915189027786255</v>
+        <v>0.6915192008018494</v>
       </c>
       <c r="JB119" t="n">
         <v>0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.4700514078140259</v>
+        <v>0.4700512588024139</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.6312121748924255</v>
+        <v>0.6312119364738464</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4888222217559814</v>
+        <v>0.4888221323490143</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4449790418148041</v>
+        <v>0.4449789524078369</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.4388045370578766</v>
+        <v>0.4388044476509094</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.6288791298866272</v>
+        <v>0.6288790106773376</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.1599999999999997</v>
